--- a/result/first_infection_DA_2023/02_dispersal_cohorts.xlsx
+++ b/result/first_infection_DA_2023/02_dispersal_cohorts.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D150"/>
+  <dimension ref="A1:D200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.264451526493378</v>
+        <v>0.3286267074389452</v>
       </c>
     </row>
     <row r="3">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.08006930323592389</v>
+        <v>0.1517509005737424</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45017.54166666666</v>
+        <v>45015.91666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1018944395822936</v>
+        <v>0.01066020385624379</v>
       </c>
     </row>
     <row r="5">
@@ -507,7 +507,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45018.04166666666</v>
+        <v>45017.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8241890302460041</v>
+        <v>0.1046909188464042</v>
       </c>
     </row>
     <row r="6">
@@ -523,7 +523,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45019</v>
+        <v>45018.04166666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8142138367126522</v>
+        <v>0.8881355561117744</v>
       </c>
     </row>
     <row r="7">
@@ -539,7 +539,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45020</v>
+        <v>45019</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7839141863550959</v>
+        <v>0.8656055676210567</v>
       </c>
     </row>
     <row r="8">
@@ -555,7 +555,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45021.20833333334</v>
+        <v>45020</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7704180204365936</v>
+        <v>0.8358568899928417</v>
       </c>
     </row>
     <row r="9">
@@ -571,7 +571,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45025.70833333334</v>
+        <v>45021.20833333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.0107658648222532</v>
+        <v>0.7704180204365936</v>
       </c>
     </row>
     <row r="10">
@@ -587,7 +587,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45027.20833333334</v>
+        <v>45025.70833333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.923767993334864</v>
+        <v>0.02199181181585527</v>
       </c>
     </row>
     <row r="11">
@@ -603,7 +603,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45028.375</v>
+        <v>45027.20833333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3718349210312757</v>
+        <v>0.923767993334864</v>
       </c>
     </row>
     <row r="12">
@@ -619,7 +619,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45029</v>
+        <v>45028.375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7159850436389711</v>
+        <v>0.4113891769452526</v>
       </c>
     </row>
     <row r="13">
@@ -635,7 +635,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45030</v>
+        <v>45029</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.8567889236903758</v>
+        <v>0.8615289531116374</v>
       </c>
     </row>
     <row r="14">
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45031.125</v>
+        <v>45030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.5406350562538148</v>
+        <v>0.8726070393807279</v>
       </c>
     </row>
     <row r="15">
@@ -667,7 +667,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45033</v>
+        <v>45031.125</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.5705874151499507</v>
+        <v>0.7893043911162356</v>
       </c>
     </row>
     <row r="16">
@@ -683,7 +683,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45034</v>
+        <v>45032.58333333334</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.7550603207627554</v>
+        <v>0.0578564314299856</v>
       </c>
     </row>
     <row r="17">
@@ -699,7 +699,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45035</v>
+        <v>45033</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.7581471794007614</v>
+        <v>0.7990500998486776</v>
       </c>
     </row>
     <row r="18">
@@ -715,7 +715,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45036.70833333334</v>
+        <v>45034</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.01759465481976376</v>
+        <v>0.7791309506412825</v>
       </c>
     </row>
     <row r="19">
@@ -731,7 +731,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45037.45833333334</v>
+        <v>45035</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.1529568517168902</v>
+        <v>0.7581471794007614</v>
       </c>
     </row>
     <row r="20">
@@ -747,7 +747,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45038</v>
+        <v>45036.70833333334</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.3883027323855677</v>
+        <v>0.03138770665627771</v>
       </c>
     </row>
     <row r="21">
@@ -763,7 +763,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45039</v>
+        <v>45037.45833333334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.5599045777057478</v>
+        <v>0.1722542026250431</v>
       </c>
     </row>
     <row r="22">
@@ -779,7 +779,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45044</v>
+        <v>45038</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7816114217717186</v>
+        <v>0.6621118188732632</v>
       </c>
     </row>
     <row r="23">
@@ -795,15 +795,15 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45045</v>
+        <v>45039</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.6937569162688637</v>
+        <v>0.7703885826296796</v>
       </c>
     </row>
     <row r="24">
@@ -811,7 +811,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45048</v>
+        <v>45040</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.4463706748202665</v>
+        <v>0.717014921196911</v>
       </c>
     </row>
     <row r="25">
@@ -827,7 +827,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45049</v>
+        <v>45041</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6731343810115171</v>
+        <v>0.4209447269324219</v>
       </c>
     </row>
     <row r="26">
@@ -843,7 +843,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45050</v>
+        <v>45042.45833333334</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.7338449283736989</v>
+        <v>0.06613953850598017</v>
       </c>
     </row>
     <row r="27">
@@ -859,7 +859,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45056</v>
+        <v>45043.33333333334</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.8183409699875566</v>
+        <v>0.4862631796429971</v>
       </c>
     </row>
     <row r="28">
@@ -875,7 +875,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45057</v>
+        <v>45044</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.7943311960161789</v>
+        <v>0.8672504841013907</v>
       </c>
     </row>
     <row r="29">
@@ -891,15 +891,15 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45061.58333333334</v>
+        <v>45045</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.06944073186947104</v>
+        <v>0.7926713901809458</v>
       </c>
     </row>
     <row r="30">
@@ -907,7 +907,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45062</v>
+        <v>45047.54166666666</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.7715216479078042</v>
+        <v>0.05577418995150248</v>
       </c>
     </row>
     <row r="31">
@@ -923,7 +923,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45063</v>
+        <v>45048</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.6759325444606857</v>
+        <v>0.7870664711710589</v>
       </c>
     </row>
     <row r="32">
@@ -939,7 +939,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45064</v>
+        <v>45049</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.7164646429690098</v>
+        <v>0.8345592687386821</v>
       </c>
     </row>
     <row r="33">
@@ -955,7 +955,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45065.66666666666</v>
+        <v>45050</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.0298752885094219</v>
+        <v>0.7629377775008915</v>
       </c>
     </row>
     <row r="34">
@@ -971,7 +971,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45066.375</v>
+        <v>45051</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.3440840089069567</v>
+        <v>0.6804273858161759</v>
       </c>
     </row>
     <row r="35">
@@ -987,7 +987,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45067</v>
+        <v>45052.125</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.3543282485834478</v>
+        <v>0.5739765517908274</v>
       </c>
     </row>
     <row r="36">
@@ -1003,7 +1003,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45068</v>
+        <v>45053</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.5174058482945865</v>
+        <v>0.6761644805537534</v>
       </c>
     </row>
     <row r="37">
@@ -1019,7 +1019,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45071.29166666666</v>
+        <v>45055.91666666666</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.6978972205447036</v>
+        <v>0.01410477386438957</v>
       </c>
     </row>
     <row r="38">
@@ -1035,7 +1035,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45072</v>
+        <v>45056</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.5227283033999227</v>
+        <v>0.8937175375651922</v>
       </c>
     </row>
     <row r="39">
@@ -1051,7 +1051,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45073</v>
+        <v>45057</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.6267559856969777</v>
+        <v>0.7943311960161789</v>
       </c>
     </row>
     <row r="40">
@@ -1067,7 +1067,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45074</v>
+        <v>45058</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.5665742628368845</v>
+        <v>0.5713737731251332</v>
       </c>
     </row>
     <row r="41">
@@ -1083,7 +1083,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45075</v>
+        <v>45061.58333333334</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.5655590533169682</v>
+        <v>0.07592783349669273</v>
       </c>
     </row>
     <row r="42">
@@ -1099,7 +1099,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45078.58333333334</v>
+        <v>45062</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9.258410523939776e-05</v>
+        <v>0.8283534187698821</v>
       </c>
     </row>
     <row r="43">
@@ -1115,15 +1115,15 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45083.125</v>
+        <v>45063</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.6917761456151825</v>
+        <v>0.6926690699636814</v>
       </c>
     </row>
     <row r="44">
@@ -1131,7 +1131,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45086.33333333334</v>
+        <v>45064</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.4171010984690052</v>
+        <v>0.7398499662233851</v>
       </c>
     </row>
     <row r="45">
@@ -1147,7 +1147,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45087.45833333334</v>
+        <v>45065.66666666666</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.1738996025020755</v>
+        <v>0.03209743055873404</v>
       </c>
     </row>
     <row r="46">
@@ -1163,7 +1163,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45088.70833333334</v>
+        <v>45066.375</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.04025198941890957</v>
+        <v>0.354728370422097</v>
       </c>
     </row>
     <row r="47">
@@ -1179,7 +1179,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45090.33333333334</v>
+        <v>45067</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.3817319814351726</v>
+        <v>0.5597540279550377</v>
       </c>
     </row>
     <row r="48">
@@ -1195,7 +1195,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45093.41666666666</v>
+        <v>45068</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.2173202622756278</v>
+        <v>0.5965773646522328</v>
       </c>
     </row>
     <row r="49">
@@ -1211,7 +1211,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>45094</v>
+        <v>45069</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.5182324313187221</v>
+        <v>0.5386904991583538</v>
       </c>
     </row>
     <row r="50">
@@ -1227,7 +1227,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45095</v>
+        <v>45070</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.4815848404668895</v>
+        <v>0.8939151801211785</v>
       </c>
     </row>
     <row r="51">
@@ -1243,7 +1243,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45096</v>
+        <v>45071.29166666666</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.5530270420539736</v>
+        <v>0.7831134797167016</v>
       </c>
     </row>
     <row r="52">
@@ -1259,7 +1259,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45097.5</v>
+        <v>45072</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.1102199754905382</v>
+        <v>0.6842290571369254</v>
       </c>
     </row>
     <row r="53">
@@ -1275,15 +1275,15 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45098.08333333334</v>
+        <v>45073</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.7462779234901163</v>
+        <v>0.6530968085818081</v>
       </c>
     </row>
     <row r="54">
@@ -1291,15 +1291,15 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45099.125</v>
+        <v>45074</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.7745037153369109</v>
+        <v>0.6506418200906873</v>
       </c>
     </row>
     <row r="55">
@@ -1307,15 +1307,15 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45100.66666666666</v>
+        <v>45075</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.03278862097539088</v>
+        <v>0.6204240619280972</v>
       </c>
     </row>
     <row r="56">
@@ -1323,15 +1323,15 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45103.29166666666</v>
+        <v>45078.58333333334</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.8265334692658969</v>
+        <v>0.002734518641047927</v>
       </c>
     </row>
     <row r="57">
@@ -1339,7 +1339,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>45104.45833333334</v>
+        <v>45079</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.1708567089189124</v>
+        <v>0.4770436534925134</v>
       </c>
     </row>
     <row r="58">
@@ -1355,7 +1355,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>45105</v>
+        <v>45080</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.5961201597826744</v>
+        <v>0.4195132611639111</v>
       </c>
     </row>
     <row r="59">
@@ -1371,7 +1371,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>45106</v>
+        <v>45081</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.467984338151005</v>
+        <v>0.3617524818886424</v>
       </c>
     </row>
     <row r="60">
@@ -1387,7 +1387,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>45107</v>
+        <v>45082</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.4852637821192718</v>
+        <v>0.5450292989057662</v>
       </c>
     </row>
     <row r="61">
@@ -1403,15 +1403,15 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>45108</v>
+        <v>45083.125</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.3733239870827553</v>
+        <v>0.7091857659565337</v>
       </c>
     </row>
     <row r="62">
@@ -1419,7 +1419,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>45110</v>
+        <v>45084.5</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.3886051083285024</v>
+        <v>0.127832841781612</v>
       </c>
     </row>
     <row r="63">
@@ -1435,7 +1435,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>45111</v>
+        <v>45085.375</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.5290365368057712</v>
+        <v>0.3180551046245234</v>
       </c>
     </row>
     <row r="64">
@@ -1451,7 +1451,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>45112</v>
+        <v>45086.33333333334</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.5332975194335815</v>
+        <v>0.4698603263405868</v>
       </c>
     </row>
     <row r="65">
@@ -1467,7 +1467,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>45113</v>
+        <v>45087.45833333334</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.3529295646553393</v>
+        <v>0.1911109894201827</v>
       </c>
     </row>
     <row r="66">
@@ -1483,7 +1483,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45114</v>
+        <v>45088.70833333334</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.3670188037218977</v>
+        <v>0.04025198941890957</v>
       </c>
     </row>
     <row r="67">
@@ -1499,7 +1499,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45115</v>
+        <v>45090.33333333334</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.3321097017409037</v>
+        <v>0.4417808023428184</v>
       </c>
     </row>
     <row r="68">
@@ -1515,7 +1515,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>45116</v>
+        <v>45091.41666666666</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.3130445132860514</v>
+        <v>0.2473929241504459</v>
       </c>
     </row>
     <row r="69">
@@ -1531,7 +1531,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>45117</v>
+        <v>45092.625</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.3276178974402142</v>
+        <v>0.05350698348292302</v>
       </c>
     </row>
     <row r="70">
@@ -1547,7 +1547,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>45119</v>
+        <v>45093.41666666666</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.3953635962426745</v>
+        <v>0.2314279133440011</v>
       </c>
     </row>
     <row r="71">
@@ -1563,7 +1563,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>45122.04166666666</v>
+        <v>45094</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.5184804532445948</v>
+        <v>0.606905353643908</v>
       </c>
     </row>
     <row r="72">
@@ -1579,7 +1579,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>45125</v>
+        <v>45095</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.3383912729294802</v>
+        <v>0.5900729012000437</v>
       </c>
     </row>
     <row r="73">
@@ -1595,7 +1595,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>45126</v>
+        <v>45096</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.7258337623408609</v>
+        <v>0.6224313445914914</v>
       </c>
     </row>
     <row r="74">
@@ -1611,15 +1611,15 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>45127.58333333334</v>
+        <v>45097.5</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.06141189102985795</v>
+        <v>0.1113385840350721</v>
       </c>
     </row>
     <row r="75">
@@ -1627,15 +1627,15 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>45128.45833333334</v>
+        <v>45098.08333333334</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.1603656263270279</v>
+        <v>0.7482475647922768</v>
       </c>
     </row>
     <row r="76">
@@ -1643,15 +1643,15 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>45129.29166666666</v>
+        <v>45099.125</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.5905167663357545</v>
+        <v>0.7745037153369109</v>
       </c>
     </row>
     <row r="77">
@@ -1659,15 +1659,15 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>45130</v>
+        <v>45100.66666666666</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.4925105549355235</v>
+        <v>0.03278862097539088</v>
       </c>
     </row>
     <row r="78">
@@ -1675,15 +1675,15 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>45131</v>
+        <v>45103.29166666666</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.4367093377545327</v>
+        <v>0.8265334692658969</v>
       </c>
     </row>
     <row r="79">
@@ -1691,7 +1691,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>45133.08333333334</v>
+        <v>45104.45833333334</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.4341490446899824</v>
+        <v>0.1784677424165042</v>
       </c>
     </row>
     <row r="80">
@@ -1707,7 +1707,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>45135.58333333334</v>
+        <v>45105</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.05125426288749041</v>
+        <v>0.685657503775447</v>
       </c>
     </row>
     <row r="81">
@@ -1723,7 +1723,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>45137.5</v>
+        <v>45106</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.08845711446832105</v>
+        <v>0.6476909649128586</v>
       </c>
     </row>
     <row r="82">
@@ -1739,7 +1739,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>45138.16666666666</v>
+        <v>45107</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.6528002445384384</v>
+        <v>0.5737058243592534</v>
       </c>
     </row>
     <row r="83">
@@ -1755,7 +1755,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>45139.54166666666</v>
+        <v>45108</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.08420418120547568</v>
+        <v>0.4928075363939755</v>
       </c>
     </row>
     <row r="84">
@@ -1771,7 +1771,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>45140.75</v>
+        <v>45109</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.01720557915300356</v>
+        <v>0.4660188310820785</v>
       </c>
     </row>
     <row r="85">
@@ -1787,7 +1787,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>45142.41666666666</v>
+        <v>45110</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.2385078335228359</v>
+        <v>0.5229094722504658</v>
       </c>
     </row>
     <row r="86">
@@ -1803,15 +1803,15 @@
         <v>84</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>45143.625</v>
+        <v>45111</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.03891585648216109</v>
+        <v>0.571862002431201</v>
       </c>
     </row>
     <row r="87">
@@ -1819,7 +1819,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>45145.54166666666</v>
+        <v>45112</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.07666762926278607</v>
+        <v>0.5843663813775508</v>
       </c>
     </row>
     <row r="88">
@@ -1835,7 +1835,7 @@
         <v>86</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>45146.54166666666</v>
+        <v>45113</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.07973986953517884</v>
+        <v>0.5787128204873239</v>
       </c>
     </row>
     <row r="89">
@@ -1851,7 +1851,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>45147.625</v>
+        <v>45114</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.0399085373347669</v>
+        <v>0.5082810484433229</v>
       </c>
     </row>
     <row r="90">
@@ -1867,15 +1867,15 @@
         <v>88</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>45149.625</v>
+        <v>45115</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.04400501987162795</v>
+        <v>0.4438340756000065</v>
       </c>
     </row>
     <row r="91">
@@ -1883,15 +1883,15 @@
         <v>89</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>45153.58333333334</v>
+        <v>45116</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.05789093868140034</v>
+        <v>0.4582923648454913</v>
       </c>
     </row>
     <row r="92">
@@ -1899,15 +1899,15 @@
         <v>90</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>45156.125</v>
+        <v>45117</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.649295716503175</v>
+        <v>0.5073938814270813</v>
       </c>
     </row>
     <row r="93">
@@ -1915,7 +1915,7 @@
         <v>91</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>45158.75</v>
+        <v>45118</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.01435951074831754</v>
+        <v>0.4974666295907658</v>
       </c>
     </row>
     <row r="94">
@@ -1931,7 +1931,7 @@
         <v>92</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>45159.33333333334</v>
+        <v>45119</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.4421949915088625</v>
+        <v>0.4724760143104735</v>
       </c>
     </row>
     <row r="95">
@@ -1947,15 +1947,15 @@
         <v>93</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>45161.20833333334</v>
+        <v>45120</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.6527214381562265</v>
+        <v>0.4125749372870358</v>
       </c>
     </row>
     <row r="96">
@@ -1963,7 +1963,7 @@
         <v>94</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>45162.83333333334</v>
+        <v>45121</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.01411244117018298</v>
+        <v>0.4634936090278413</v>
       </c>
     </row>
     <row r="97">
@@ -1979,15 +1979,15 @@
         <v>95</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>45163.04166666666</v>
+        <v>45122.04166666666</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.7244698392707946</v>
+        <v>0.6208634042023173</v>
       </c>
     </row>
     <row r="98">
@@ -1995,7 +1995,7 @@
         <v>96</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>45164.16666666666</v>
+        <v>45123.375</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.6015592762313129</v>
+        <v>0.1203669267240603</v>
       </c>
     </row>
     <row r="99">
@@ -2011,7 +2011,7 @@
         <v>97</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>45165</v>
+        <v>45125</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.5664526993166028</v>
+        <v>0.7121378607263259</v>
       </c>
     </row>
     <row r="100">
@@ -2027,7 +2027,7 @@
         <v>98</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>45166.375</v>
+        <v>45126</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.2955426548071955</v>
+        <v>0.7258337623408609</v>
       </c>
     </row>
     <row r="101">
@@ -2043,15 +2043,15 @@
         <v>99</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>45174.45833333334</v>
+        <v>45127.58333333334</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.1506919910577908</v>
+        <v>0.06141189102985795</v>
       </c>
     </row>
     <row r="102">
@@ -2059,7 +2059,7 @@
         <v>100</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>45175.41666666666</v>
+        <v>45128.45833333334</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.1371045467742358</v>
+        <v>0.160317938402775</v>
       </c>
     </row>
     <row r="103">
@@ -2075,7 +2075,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>45176.45833333334</v>
+        <v>45129.29166666666</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.1766038224795521</v>
+        <v>0.5954392518930719</v>
       </c>
     </row>
     <row r="104">
@@ -2091,7 +2091,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>45177.70833333334</v>
+        <v>45130</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.02345241541426114</v>
+        <v>0.5386439628778071</v>
       </c>
     </row>
     <row r="105">
@@ -2107,7 +2107,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>45178.41666666666</v>
+        <v>45131</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.2446371047754279</v>
+        <v>0.5143664708222292</v>
       </c>
     </row>
     <row r="106">
@@ -2123,7 +2123,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>45179.375</v>
+        <v>45132</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.3692786480533382</v>
+        <v>0.5024490974189919</v>
       </c>
     </row>
     <row r="107">
@@ -2139,7 +2139,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>45180.375</v>
+        <v>45133.08333333334</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.344284260150898</v>
+        <v>0.5229377236251798</v>
       </c>
     </row>
     <row r="108">
@@ -2155,7 +2155,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>45181.41666666666</v>
+        <v>45135.58333333334</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.2434031977497781</v>
+        <v>0.05572152211946962</v>
       </c>
     </row>
     <row r="109">
@@ -2171,15 +2171,15 @@
         <v>107</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>45182.33333333334</v>
+        <v>45136.66666666666</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.4568182417063411</v>
+        <v>0.01931728686724835</v>
       </c>
     </row>
     <row r="110">
@@ -2187,7 +2187,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>45183</v>
+        <v>45137.5</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.6233189121674289</v>
+        <v>0.09605864921252411</v>
       </c>
     </row>
     <row r="111">
@@ -2203,7 +2203,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>45184.41666666666</v>
+        <v>45138.16666666666</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.2760537247048586</v>
+        <v>0.6562686342005746</v>
       </c>
     </row>
     <row r="112">
@@ -2219,15 +2219,15 @@
         <v>110</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>45186.58333333334</v>
+        <v>45139.54166666666</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.06008613200137244</v>
+        <v>0.08420418120547568</v>
       </c>
     </row>
     <row r="113">
@@ -2235,7 +2235,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>45187.625</v>
+        <v>45140.75</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.04618426022522749</v>
+        <v>0.01721372968531962</v>
       </c>
     </row>
     <row r="114">
@@ -2251,7 +2251,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>45188.20833333334</v>
+        <v>45142.41666666666</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.6714665501609469</v>
+        <v>0.2389303509954632</v>
       </c>
     </row>
     <row r="115">
@@ -2267,15 +2267,15 @@
         <v>113</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>45189</v>
+        <v>45143.625</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.648567916327826</v>
+        <v>0.03891585648216109</v>
       </c>
     </row>
     <row r="116">
@@ -2283,7 +2283,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>45191.70833333334</v>
+        <v>45145.54166666666</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.02300076133178438</v>
+        <v>0.07666762926278607</v>
       </c>
     </row>
     <row r="117">
@@ -2299,7 +2299,7 @@
         <v>115</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>45192.5</v>
+        <v>45146.54166666666</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.1098140604271629</v>
+        <v>0.08075304655865805</v>
       </c>
     </row>
     <row r="118">
@@ -2315,7 +2315,7 @@
         <v>116</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>45194.54166666666</v>
+        <v>45147.625</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.08575658882401108</v>
+        <v>0.04017322984771839</v>
       </c>
     </row>
     <row r="119">
@@ -2331,15 +2331,15 @@
         <v>117</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>45195.375</v>
+        <v>45149.625</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.3392173070268115</v>
+        <v>0.04412424297431948</v>
       </c>
     </row>
     <row r="120">
@@ -2347,15 +2347,15 @@
         <v>118</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>45196.41666666666</v>
+        <v>45153.58333333334</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.2245742327369452</v>
+        <v>0.05825113305052005</v>
       </c>
     </row>
     <row r="121">
@@ -2363,15 +2363,15 @@
         <v>119</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>45198.625</v>
+        <v>45156.125</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.04712504193616773</v>
+        <v>0.6496656592785949</v>
       </c>
     </row>
     <row r="122">
@@ -2379,7 +2379,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>45200.375</v>
+        <v>45158.75</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.007757031102490212</v>
+        <v>0.01435951074831754</v>
       </c>
     </row>
     <row r="123">
@@ -2395,7 +2395,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>45201.66666666666</v>
+        <v>45159.33333333334</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.02932859232025072</v>
+        <v>0.4421949915088625</v>
       </c>
     </row>
     <row r="124">
@@ -2411,15 +2411,15 @@
         <v>122</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>45204.125</v>
+        <v>45161.20833333334</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.4614384983268102</v>
+        <v>0.6986763297350767</v>
       </c>
     </row>
     <row r="125">
@@ -2427,7 +2427,7 @@
         <v>123</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>45214.41666666666</v>
+        <v>45162.83333333334</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.1739050065975179</v>
+        <v>0.01468904801849042</v>
       </c>
     </row>
     <row r="126">
@@ -2443,15 +2443,15 @@
         <v>124</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>45224.70833333334</v>
+        <v>45163.04166666666</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.0006307154774340395</v>
+        <v>0.7244698392707946</v>
       </c>
     </row>
     <row r="127">
@@ -2459,7 +2459,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>45225.79166666666</v>
+        <v>45164.16666666666</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.01684977786099822</v>
+        <v>0.6224313445914914</v>
       </c>
     </row>
     <row r="128">
@@ -2475,7 +2475,7 @@
         <v>126</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>45228.54166666666</v>
+        <v>45165</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.06723182603082235</v>
+        <v>0.6121261480621042</v>
       </c>
     </row>
     <row r="129">
@@ -2491,7 +2491,7 @@
         <v>127</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>45229.45833333334</v>
+        <v>45166.375</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.1737264177688382</v>
+        <v>0.3468918651892237</v>
       </c>
     </row>
     <row r="130">
@@ -2507,7 +2507,7 @@
         <v>128</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>45232.54166666666</v>
+        <v>45168.375</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>4.881178496226186e-05</v>
+        <v>0.3066697333517893</v>
       </c>
     </row>
     <row r="131">
@@ -2523,7 +2523,7 @@
         <v>129</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>45233</v>
+        <v>45169.375</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.7361270431744097</v>
+        <v>0.2615995273338957</v>
       </c>
     </row>
     <row r="132">
@@ -2539,7 +2539,7 @@
         <v>130</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>45234.125</v>
+        <v>45170.41666666666</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.7319940893766035</v>
+        <v>0.1854244941808753</v>
       </c>
     </row>
     <row r="133">
@@ -2555,7 +2555,7 @@
         <v>131</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>45235</v>
+        <v>45172</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.7581471794007614</v>
+        <v>0.7763751147077492</v>
       </c>
     </row>
     <row r="134">
@@ -2571,7 +2571,7 @@
         <v>132</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>45236.125</v>
+        <v>45173</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.5361298788414989</v>
+        <v>0.8635899924175149</v>
       </c>
     </row>
     <row r="135">
@@ -2587,7 +2587,7 @@
         <v>133</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>45238.5</v>
+        <v>45174.45833333334</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.1202380934609337</v>
+        <v>0.2010923050198854</v>
       </c>
     </row>
     <row r="136">
@@ -2603,7 +2603,7 @@
         <v>134</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>45239.04166666666</v>
+        <v>45175.41666666666</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.849983260921445</v>
+        <v>0.2558940564892063</v>
       </c>
     </row>
     <row r="137">
@@ -2619,7 +2619,7 @@
         <v>135</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>45240.20833333334</v>
+        <v>45176.45833333334</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.7990500998486776</v>
+        <v>0.1843305745227971</v>
       </c>
     </row>
     <row r="138">
@@ -2635,7 +2635,7 @@
         <v>136</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>45241</v>
+        <v>45177.70833333334</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.621437721384355</v>
+        <v>0.0239555360101412</v>
       </c>
     </row>
     <row r="139">
@@ -2651,7 +2651,7 @@
         <v>137</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>45245.75</v>
+        <v>45178.41666666666</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.00482280766159921</v>
+        <v>0.2563573548314078</v>
       </c>
     </row>
     <row r="140">
@@ -2667,7 +2667,7 @@
         <v>138</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>45253.625</v>
+        <v>45179.375</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.03420821836030444</v>
+        <v>0.3720382610486022</v>
       </c>
     </row>
     <row r="141">
@@ -2683,7 +2683,7 @@
         <v>139</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>45254.5</v>
+        <v>45180.375</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.08696171319376773</v>
+        <v>0.3540900645894658</v>
       </c>
     </row>
     <row r="142">
@@ -2699,7 +2699,7 @@
         <v>140</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>45259.54166666666</v>
+        <v>45181.41666666666</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.0008182449989495906</v>
+        <v>0.2434031977497781</v>
       </c>
     </row>
     <row r="143">
@@ -2715,7 +2715,7 @@
         <v>141</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>45268.41666666666</v>
+        <v>45182.33333333334</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.0006950683162457236</v>
+        <v>0.5404625806451197</v>
       </c>
     </row>
     <row r="144">
@@ -2731,7 +2731,7 @@
         <v>142</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>45269</v>
+        <v>45183</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.7130513844699926</v>
+        <v>0.8883660338527809</v>
       </c>
     </row>
     <row r="145">
@@ -2747,7 +2747,7 @@
         <v>143</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>45270</v>
+        <v>45184.41666666666</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.7973851888715399</v>
+        <v>0.2951005532237448</v>
       </c>
     </row>
     <row r="146">
@@ -2763,15 +2763,15 @@
         <v>144</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>45271</v>
+        <v>45186.58333333334</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.7978228987499522</v>
+        <v>0.06068822058170995</v>
       </c>
     </row>
     <row r="147">
@@ -2779,7 +2779,7 @@
         <v>145</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>45274</v>
+        <v>45187.625</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.8645402050441734</v>
+        <v>0.04618426022522749</v>
       </c>
     </row>
     <row r="148">
@@ -2795,7 +2795,7 @@
         <v>146</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>45275</v>
+        <v>45188.20833333334</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.7969811489837747</v>
+        <v>0.6872347394579964</v>
       </c>
     </row>
     <row r="149">
@@ -2811,7 +2811,7 @@
         <v>147</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>45289.54166666666</v>
+        <v>45189</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.02848118122196406</v>
+        <v>0.679682646903372</v>
       </c>
     </row>
     <row r="150">
@@ -2827,15 +2827,815 @@
         <v>148</v>
       </c>
       <c r="B150" s="2" t="n">
+        <v>45191.70833333334</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0.02402022967423574</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>45192.5</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0.1213558223891338</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>45194.54166666666</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0.09368689676360653</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>45195.375</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0.3544746702747428</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>45196.41666666666</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0.2454473453886319</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>45198.625</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0.04715989138071685</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>45200.375</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0.3308704879120362</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>45201.66666666666</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0.03207236172702385</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>45204.125</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0.6569591776438988</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>45212.41666666666</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0.2992511369576356</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>45213.41666666666</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0.2395283839065387</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>45214.41666666666</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0.2675991065579381</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>45216.75</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>0.0008272702446923879</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>45218</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0.8454277149803363</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>45219</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0.5189523842159304</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>45224.70833333334</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0.03169651446403229</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" s="2" t="n">
+        <v>45225.79166666666</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>0.02529653507165338</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>45226.66666666666</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>0.0383228270282464</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" s="2" t="n">
+        <v>45227.20833333334</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0.6302772952790135</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" s="2" t="n">
+        <v>45228.54166666666</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0.09700997289156472</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" s="2" t="n">
+        <v>45229.45833333334</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>0.1986257507490876</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" s="2" t="n">
+        <v>45232.54166666666</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>0.002298029748659436</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" s="2" t="n">
+        <v>45233</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>0.8603868639686059</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" s="2" t="n">
+        <v>45234.125</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>0.8421583287150334</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" s="2" t="n">
+        <v>45235</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>0.8401002062108245</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" s="2" t="n">
+        <v>45236.125</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>0.8193632212256853</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" s="2" t="n">
+        <v>45237.125</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>0.7369442151515647</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" s="2" t="n">
+        <v>45238.5</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>0.146620141021471</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" s="2" t="n">
+        <v>45239.04166666666</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>0.8649387607868022</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" s="2" t="n">
+        <v>45240.20833333334</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>0.8558105793512131</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" s="2" t="n">
+        <v>45241</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>0.7909005980802465</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" s="2" t="n">
+        <v>45245.75</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>0.00607195760355453</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" s="2" t="n">
+        <v>45246</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>0.3913234768204104</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" s="2" t="n">
+        <v>45253.625</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>0.04876857870535003</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" s="2" t="n">
+        <v>45254.5</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>0.1046914098264272</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" s="2" t="n">
+        <v>45255.5</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>0.1166248937248589</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" s="2" t="n">
+        <v>45259.54166666666</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>0.08046048441578339</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" s="2" t="n">
+        <v>45260</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>0.783014338048681</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" s="2" t="n">
+        <v>45264.41666666666</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>0.1125785326443946</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>187</v>
+      </c>
+      <c r="B189" s="2" t="n">
+        <v>45266.375</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>0.3142302663712337</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" s="2" t="n">
+        <v>45268.41666666666</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>0.001394560142867532</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" s="2" t="n">
+        <v>45269</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>0.8956371329971368</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" s="2" t="n">
+        <v>45270</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>0.8852807011673461</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" s="2" t="n">
+        <v>45271</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>0.9023203560404595</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>0.3789982256810178</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" s="2" t="n">
+        <v>45273.5</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>0.1026350886385946</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" s="2" t="n">
+        <v>45274</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>0.9088217226744403</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" s="2" t="n">
+        <v>45275</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>0.8644433625958958</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" s="2" t="n">
+        <v>45288.625</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>0.006483347878061178</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" s="2" t="n">
+        <v>45289.54166666666</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>0.05767131497984154</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" s="2" t="n">
         <v>45291.95833333334</v>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>wind</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>0.0001799024431382388</v>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>0.01488086563695213</v>
       </c>
     </row>
   </sheetData>
